--- a/EntreesCDA/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/EntreesCDA/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T13:12:24+00:00</t>
+    <t>2026-04-20T13:35:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
